--- a/assets/templates/Registro_Primaria.xlsx
+++ b/assets/templates/Registro_Primaria.xlsx
@@ -2517,7 +2517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A7:BQ54"/>
+  <dimension ref="A7:AD25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col width="2.6640625" customWidth="1" style="147" min="1" max="39"/>
@@ -2554,10 +2554,6 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
     <row r="23" ht="17.4" customHeight="1" s="147">
       <c r="Q23" s="172" t="n"/>
     </row>
@@ -2567,35 +2563,6 @@
     <row r="25" ht="17.4" customHeight="1" s="147">
       <c r="Q25" s="172" t="n"/>
     </row>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="L7:T7"/>

--- a/assets/templates/Registro_Primaria.xlsx
+++ b/assets/templates/Registro_Primaria.xlsx
@@ -2587,7 +2587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B3:BQ56"/>
+  <dimension ref="A1:Q56"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col width="0.44140625" customWidth="1" style="147" min="1" max="1"/>
@@ -2606,6 +2606,8 @@
     <col width="4" customWidth="1" style="147" min="17" max="17"/>
   </cols>
   <sheetData>
+    <row r="1"/>
+    <row r="2"/>
     <row r="3" ht="18" customHeight="1" s="147">
       <c r="B3" s="160" t="inlineStr">
         <is>
@@ -2632,18 +2634,10 @@
       <c r="Q4" s="12" t="n"/>
     </row>
     <row r="5">
-      <c r="B5" s="146" t="inlineStr">
-        <is>
-          <t>ESCUELA CERRO CACICON</t>
-        </is>
-      </c>
+      <c r="B5" s="146" t="n"/>
     </row>
     <row r="6">
-      <c r="B6" s="146" t="inlineStr">
-        <is>
-          <t>CACICON, COMARCA NGABE BUGLE</t>
-        </is>
-      </c>
+      <c r="B6" s="146" t="n"/>
     </row>
     <row r="7">
       <c r="B7" s="146" t="inlineStr">
@@ -2743,11 +2737,7 @@
       </c>
       <c r="J11" s="157" t="n"/>
       <c r="K11" s="145" t="n"/>
-      <c r="L11" s="163" t="inlineStr">
-        <is>
-          <t>ELMER TUGRI</t>
-        </is>
-      </c>
+      <c r="L11" s="163" t="n"/>
       <c r="M11" s="157" t="n"/>
       <c r="N11" s="157" t="n"/>
       <c r="O11" s="157" t="n"/>
@@ -5422,7 +5412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BQ137"/>
+  <dimension ref="A1:R137"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="28.77734375" customWidth="1" style="147" min="1" max="1"/>
@@ -9019,7 +9009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BQ152"/>
+  <dimension ref="A1:P152"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="5" customWidth="1" style="147" min="1" max="1"/>
@@ -9099,7 +9089,7 @@
     <row r="4" ht="16.05" customHeight="1" s="147">
       <c r="A4" s="252" t="inlineStr">
         <is>
-          <t>Docente: Elmer Tugri  |  Primaria Multigrado  |  Fecha: =TEXT(TODAY(),"DD/MM/YYYY")</t>
+          <t>Docente:   |  Primaria Multigrado  |  Fecha: =TEXT(TODAY(),"DD/MM/YYYY")</t>
         </is>
       </c>
       <c r="B4" s="193" t="n"/>
@@ -9118,6 +9108,7 @@
       <c r="O4" s="193" t="n"/>
       <c r="P4" s="194" t="n"/>
     </row>
+    <row r="5"/>
     <row r="6" ht="19.95" customHeight="1" s="147">
       <c r="A6" s="247" t="inlineStr">
         <is>
@@ -9200,6 +9191,7 @@
       <c r="C11" s="122" t="n"/>
       <c r="D11" s="122" t="n"/>
     </row>
+    <row r="12"/>
     <row r="13" ht="19.95" customHeight="1" s="147">
       <c r="A13" s="247" t="inlineStr">
         <is>
@@ -12112,6 +12104,8 @@
       </c>
       <c r="F140" s="196" t="n"/>
     </row>
+    <row r="141"/>
+    <row r="142"/>
     <row r="143" ht="18" customHeight="1" s="147">
       <c r="A143" s="247" t="inlineStr">
         <is>
@@ -12134,10 +12128,11 @@
       <c r="O143" s="193" t="n"/>
       <c r="P143" s="194" t="n"/>
     </row>
+    <row r="144"/>
     <row r="145">
       <c r="A145" s="246" t="inlineStr">
         <is>
-          <t>Docente:  Elmer Tugri</t>
+          <t xml:space="preserve">Docente:  </t>
         </is>
       </c>
     </row>
@@ -12148,6 +12143,7 @@
         </is>
       </c>
     </row>
+    <row r="147"/>
     <row r="148">
       <c r="A148" s="246" t="inlineStr">
         <is>
@@ -12162,6 +12158,7 @@
         </is>
       </c>
     </row>
+    <row r="150"/>
     <row r="151">
       <c r="A151" s="246" t="inlineStr">
         <is>
@@ -12206,7 +12203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BQ134"/>
+  <dimension ref="A1:L134"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="6" customWidth="1" style="147" min="1" max="1"/>
@@ -12237,7 +12234,7 @@
     <row r="2" ht="16.05" customHeight="1" s="147">
       <c r="A2" s="255" t="inlineStr">
         <is>
-          <t>Escuela Cerro Cacicón · Prof. Elmer Tugri · Premedia Multigrado</t>
+          <t>Escuela Cerro Cacicón ·  · Premedia Multigrado</t>
         </is>
       </c>
       <c r="B2" s="193" t="n"/>
@@ -12252,6 +12249,7 @@
       <c r="K2" s="193" t="n"/>
       <c r="L2" s="194" t="n"/>
     </row>
+    <row r="3"/>
     <row r="4" ht="19.95" customHeight="1" s="147">
       <c r="A4" s="247" t="inlineStr">
         <is>
@@ -13493,6 +13491,7 @@
       <c r="D90" s="130" t="n"/>
       <c r="E90" s="130" t="n"/>
     </row>
+    <row r="91"/>
     <row r="92" ht="19.95" customHeight="1" s="147">
       <c r="A92" s="253" t="n"/>
       <c r="B92" s="193" t="n"/>
@@ -13822,7 +13821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BQ54"/>
+  <dimension ref="A1:N29"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="22" customWidth="1" style="147" min="1" max="1"/>
@@ -13853,7 +13852,7 @@
     <row r="2" ht="16.05" customHeight="1" s="147">
       <c r="A2" s="261" t="inlineStr">
         <is>
-          <t>Prof. Elmer Tugri · Escuela Cerro Cacicón · Actualización automática</t>
+          <t xml:space="preserve"> · Escuela Cerro Cacicón · Actualización automática</t>
         </is>
       </c>
       <c r="B2" s="193" t="n"/>
@@ -13870,6 +13869,7 @@
       <c r="M2" s="193" t="n"/>
       <c r="N2" s="194" t="n"/>
     </row>
+    <row r="3"/>
     <row r="4" ht="19.95" customHeight="1" s="147">
       <c r="A4" s="247" t="inlineStr">
         <is>
@@ -14004,6 +14004,8 @@
         <v/>
       </c>
     </row>
+    <row r="12"/>
+    <row r="13"/>
     <row r="14" ht="18" customHeight="1" s="147">
       <c r="A14" s="247" t="inlineStr">
         <is>
@@ -14264,31 +14266,6 @@
       <c r="M29" s="193" t="n"/>
       <c r="N29" s="194" t="n"/>
     </row>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
   </sheetData>
   <mergeCells count="19">
     <mergeCell ref="A24:N24"/>
@@ -14322,16 +14299,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ43"/>
+  <dimension ref="A4:AZ43"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col width="6.44140625" customWidth="1" style="147" min="1" max="1"/>
     <col width="1.6640625" customWidth="1" style="147" min="2" max="63"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2"/>
-    <row r="3"/>
     <row r="4" ht="18" customHeight="1" s="147">
       <c r="A4" s="175" t="inlineStr">
         <is>
@@ -14410,7 +14384,6 @@
       <c r="AX8" s="173" t="n"/>
       <c r="AY8" s="173" t="n"/>
     </row>
-    <row r="9"/>
     <row r="10" ht="19.5" customHeight="1" s="147">
       <c r="A10" t="inlineStr">
         <is>
@@ -14538,11 +14511,7 @@
       <c r="M14" s="173" t="n"/>
       <c r="N14" s="173" t="n"/>
       <c r="O14" s="173" t="n"/>
-      <c r="P14" s="173" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Elmer Tugri </t>
-        </is>
-      </c>
+      <c r="P14" s="173" t="n"/>
       <c r="Q14" s="174" t="n"/>
       <c r="R14" s="174" t="n"/>
       <c r="S14" s="174" t="n"/>
@@ -14588,11 +14557,7 @@
       </c>
       <c r="F16" s="174" t="n"/>
       <c r="G16" s="173" t="n"/>
-      <c r="H16" s="173" t="inlineStr">
-        <is>
-          <t>8-000-0000</t>
-        </is>
-      </c>
+      <c r="H16" s="173" t="n"/>
       <c r="I16" s="174" t="n"/>
       <c r="J16" s="174" t="n"/>
       <c r="K16" s="174" t="n"/>
@@ -14651,11 +14616,7 @@
       <c r="R18" s="173" t="n"/>
       <c r="S18" s="173" t="n"/>
       <c r="T18" s="173" t="n"/>
-      <c r="U18" s="173" t="inlineStr">
-        <is>
-          <t>Maestro de Grado</t>
-        </is>
-      </c>
+      <c r="U18" s="173" t="n"/>
       <c r="V18" s="174" t="n"/>
       <c r="W18" s="174" t="n"/>
       <c r="X18" s="174" t="n"/>
@@ -14771,11 +14732,7 @@
       <c r="P22" s="174" t="n"/>
       <c r="Q22" s="174" t="n"/>
       <c r="R22" s="174" t="n"/>
-      <c r="S22" s="173" t="inlineStr">
-        <is>
-          <t>Mardel Camarena</t>
-        </is>
-      </c>
+      <c r="S22" s="173" t="n"/>
       <c r="T22" s="174" t="n"/>
       <c r="U22" s="174" t="n"/>
       <c r="V22" s="174" t="n"/>
@@ -14826,11 +14783,7 @@
       <c r="Q24" s="174" t="n"/>
       <c r="R24" s="174" t="n"/>
       <c r="S24" s="174" t="n"/>
-      <c r="T24" s="173" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Jairo Marciaga </t>
-        </is>
-      </c>
+      <c r="T24" s="173" t="n"/>
       <c r="U24" s="174" t="n"/>
       <c r="V24" s="174" t="n"/>
       <c r="W24" s="174" t="n"/>
@@ -14931,11 +14884,7 @@
       <c r="N28" s="173" t="n"/>
       <c r="O28" s="173" t="n"/>
       <c r="P28" s="173" t="n"/>
-      <c r="Q28" s="173" t="inlineStr">
-        <is>
-          <t>Escuela Cerro Cacicon</t>
-        </is>
-      </c>
+      <c r="Q28" s="173" t="n"/>
       <c r="R28" s="174" t="n"/>
       <c r="S28" s="174" t="n"/>
       <c r="T28" s="174" t="n"/>
@@ -14982,9 +14931,7 @@
       </c>
       <c r="D30" s="174" t="n"/>
       <c r="E30" s="174" t="n"/>
-      <c r="F30" s="173" t="n">
-        <v>64185780</v>
-      </c>
+      <c r="F30" s="173" t="n"/>
       <c r="G30" s="174" t="n"/>
       <c r="H30" s="174" t="n"/>
       <c r="I30" s="174" t="n"/>
@@ -15004,11 +14951,7 @@
         </is>
       </c>
       <c r="AE30" s="174" t="n"/>
-      <c r="AF30" s="177" t="inlineStr">
-        <is>
-          <t>elmer.tugri7@meduca.edu.pa</t>
-        </is>
-      </c>
+      <c r="AF30" s="177" t="n"/>
       <c r="AG30" s="174" t="n"/>
       <c r="AH30" s="174" t="n"/>
       <c r="AI30" s="174" t="n"/>
@@ -15046,11 +14989,7 @@
       <c r="J32" s="173" t="n"/>
       <c r="K32" s="173" t="n"/>
       <c r="L32" s="173" t="n"/>
-      <c r="M32" s="173" t="inlineStr">
-        <is>
-          <t>Comarca Ngabe Bugle</t>
-        </is>
-      </c>
+      <c r="M32" s="173" t="n"/>
       <c r="N32" s="174" t="n"/>
       <c r="O32" s="174" t="n"/>
       <c r="P32" s="174" t="n"/>
@@ -15106,11 +15045,7 @@
       <c r="I34" s="174" t="n"/>
       <c r="J34" s="174" t="n"/>
       <c r="K34" s="174" t="n"/>
-      <c r="L34" s="173" t="inlineStr">
-        <is>
-          <t>MÜNA</t>
-        </is>
-      </c>
+      <c r="L34" s="173" t="n"/>
       <c r="M34" s="174" t="n"/>
       <c r="N34" s="174" t="n"/>
       <c r="O34" s="174" t="n"/>
@@ -15168,11 +15103,7 @@
       <c r="N36" s="174" t="n"/>
       <c r="O36" s="174" t="n"/>
       <c r="P36" s="174" t="n"/>
-      <c r="Q36" s="173" t="inlineStr">
-        <is>
-          <t>MARACA</t>
-        </is>
-      </c>
+      <c r="Q36" s="173" t="n"/>
       <c r="R36" s="174" t="n"/>
       <c r="S36" s="174" t="n"/>
       <c r="T36" s="174" t="n"/>
@@ -15226,9 +15157,7 @@
       <c r="L38" s="75" t="n"/>
       <c r="M38" s="75" t="n"/>
       <c r="N38" s="75" t="n"/>
-      <c r="O38" s="176" t="n">
-        <v>31</v>
-      </c>
+      <c r="O38" s="176" t="n"/>
       <c r="P38" s="174" t="n"/>
       <c r="Q38" s="174" t="n"/>
       <c r="R38" s="174" t="n"/>
@@ -15299,12 +15228,9 @@
     <mergeCell ref="Q28:AQ28"/>
     <mergeCell ref="AF30:AX30"/>
   </mergeCells>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AF30" r:id="rId1"/>
-  </hyperlinks>
   <pageMargins left="0.6299212598425197" right="0.2362204724409449" top="0.7480314960629921" bottom="0.7480314960629921" header="0.3149606299212598" footer="0.3149606299212598"/>
   <pageSetup orientation="portrait"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -15315,7 +15241,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X33"/>
+  <dimension ref="A2:X33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col width="1.6640625" customWidth="1" style="147" min="1" max="14"/>
@@ -15876,7 +15802,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BQ124"/>
+  <dimension ref="A1:C124"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col width="44.6640625" customWidth="1" style="147" min="1" max="1"/>
@@ -16481,9 +16407,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A4:BQ54"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <sheetData>
+    <row r="1"/>
+    <row r="2"/>
+    <row r="3"/>
     <row r="4" ht="18" customHeight="1" s="147">
       <c r="A4" s="191" t="inlineStr">
         <is>
@@ -16491,6 +16420,8 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
+    <row r="6"/>
     <row r="7" ht="25.05" customHeight="1" s="147">
       <c r="A7" s="174" t="n"/>
       <c r="B7" s="174" t="n"/>
@@ -16691,30 +16622,6 @@
     </row>
     <row r="29" ht="25.05" customHeight="1" s="147"/>
     <row r="30" ht="25.05" customHeight="1" s="147"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A4:H4"/>
@@ -16731,7 +16638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:N60"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="5" customWidth="1" style="147" min="1" max="1"/>
@@ -17135,11 +17042,7 @@
     </row>
     <row r="39"/>
     <row r="40">
-      <c r="A40" s="203" t="inlineStr">
-        <is>
-          <t>⚠ IMPORTANTE: Solo edita esta hoja para nombres. Todas las demás hojas se actualizan automáticamente.</t>
-        </is>
-      </c>
+      <c r="A40" s="203" t="n"/>
     </row>
     <row r="41"/>
     <row r="42"/>
@@ -17155,6 +17058,12 @@
     <row r="52"/>
     <row r="53"/>
     <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
   </sheetData>
   <mergeCells count="74">
     <mergeCell ref="B11:D11"/>
@@ -17243,7 +17152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BQ121"/>
+  <dimension ref="A1:Y121"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="5" customWidth="1" style="147" min="1" max="1"/>
@@ -22340,6 +22249,9 @@
       </c>
       <c r="L79" s="90" t="n"/>
     </row>
+    <row r="80"/>
+    <row r="81"/>
+    <row r="82"/>
     <row r="83">
       <c r="A83" s="205" t="inlineStr">
         <is>
@@ -24210,7 +24122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BQ138"/>
+  <dimension ref="A1:BL138"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col width="3.44140625" customWidth="1" style="147" min="1" max="1"/>
@@ -34402,6 +34314,11 @@
         <v>42</v>
       </c>
     </row>
+    <row r="131"/>
+    <row r="132"/>
+    <row r="133"/>
+    <row r="134"/>
+    <row r="135"/>
     <row r="136" ht="13.5" customHeight="1" s="147"/>
     <row r="137" ht="14.4" customHeight="1" s="147">
       <c r="A137" s="74" t="n"/>
@@ -34457,7 +34374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EE54"/>
+  <dimension ref="A1:EE48"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col width="2.77734375" bestFit="1" customWidth="1" style="147" min="1" max="1"/>
@@ -41452,12 +41369,6 @@
       <c r="EB48" s="148" t="n"/>
       <c r="EC48" s="148" t="n"/>
     </row>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
   </sheetData>
   <mergeCells count="260">
     <mergeCell ref="CA40:CA48"/>
